--- a/AutoBdc/res/PledgeFileInfo.xlsx
+++ b/AutoBdc/res/PledgeFileInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LCY\gitee\auto-work\AutoBdc\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A83ED33-E377-4362-AF10-7DD7D751ECAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED656410-5F1D-4C5E-9D9E-586C67043AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18090" yWindow="3630" windowWidth="15210" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="3825" windowWidth="15210" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pledge_img_info" sheetId="1" r:id="rId1"/>
